--- a/LubanConfig/MiniTemplate/Datas/生成数据/#阵容战力成长时间分布_2导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#阵容战力成长时间分布_2导.xlsx
@@ -91,24 +91,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -124,7 +126,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -141,20 +150,20 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,7 +623,6 @@
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <f>SUM($E$4:$E4)</f>
         <v>1</v>
       </c>
       <c r="G4" s="2">
@@ -633,11 +641,9 @@
         <v>327.5</v>
       </c>
       <c r="L4" s="2">
-        <f>$K$4*30</f>
         <v>9825</v>
       </c>
       <c r="M4" s="2">
-        <f>ROUND($L$4/($J$4/3),0)</f>
         <v>13</v>
       </c>
     </row>
@@ -655,7 +661,6 @@
         <v>2</v>
       </c>
       <c r="F5" s="2">
-        <f>SUM($E$4:$E5)</f>
         <v>3</v>
       </c>
       <c r="G5" s="2">
@@ -674,11 +679,9 @@
         <v>410</v>
       </c>
       <c r="L5" s="2">
-        <f>$K$5*30</f>
         <v>12300</v>
       </c>
       <c r="M5" s="2">
-        <f>ROUND($L$5/($J$5/3),0)</f>
         <v>14</v>
       </c>
     </row>
@@ -696,7 +699,6 @@
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <f>SUM($E$4:$E6)</f>
         <v>4</v>
       </c>
       <c r="G6" s="2">
@@ -715,11 +717,9 @@
         <v>456.8</v>
       </c>
       <c r="L6" s="2">
-        <f>$K$6*30</f>
         <v>13704</v>
       </c>
       <c r="M6" s="2">
-        <f>ROUND($L$6/($J$6/3),0)</f>
         <v>15</v>
       </c>
     </row>
@@ -737,7 +737,6 @@
         <v>1</v>
       </c>
       <c r="F7" s="2">
-        <f>SUM($E$4:$E7)</f>
         <v>5</v>
       </c>
       <c r="G7" s="2">
@@ -756,11 +755,9 @@
         <v>507.5</v>
       </c>
       <c r="L7" s="2">
-        <f>$K$7*30</f>
         <v>15225</v>
       </c>
       <c r="M7" s="2">
-        <f>ROUND($L$7/($J$7/3),0)</f>
         <v>16</v>
       </c>
     </row>
@@ -778,7 +775,6 @@
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <f>SUM($E$4:$E8)</f>
         <v>6</v>
       </c>
       <c r="G8" s="2">
@@ -797,11 +793,9 @@
         <v>562.5</v>
       </c>
       <c r="L8" s="2">
-        <f>$K$8*30</f>
         <v>16875</v>
       </c>
       <c r="M8" s="2">
-        <f>ROUND($L$8/($J$8/3),0)</f>
         <v>17</v>
       </c>
     </row>
@@ -819,7 +813,6 @@
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <f>SUM($E$4:$E9)</f>
         <v>7</v>
       </c>
       <c r="G9" s="2">
@@ -838,11 +831,9 @@
         <v>622</v>
       </c>
       <c r="L9" s="2">
-        <f>$K$9*30</f>
         <v>18660</v>
       </c>
       <c r="M9" s="2">
-        <f>ROUND($L$9/($J$9/3),0)</f>
         <v>18</v>
       </c>
     </row>
@@ -860,7 +851,6 @@
         <v>2</v>
       </c>
       <c r="F10" s="2">
-        <f>SUM($E$4:$E10)</f>
         <v>9</v>
       </c>
       <c r="G10" s="2">
@@ -879,11 +869,9 @@
         <v>755.7</v>
       </c>
       <c r="L10" s="2">
-        <f>$K$10*30</f>
         <v>22671</v>
       </c>
       <c r="M10" s="2">
-        <f>ROUND($L$10/($J$10/3),0)</f>
         <v>20</v>
       </c>
     </row>
@@ -901,7 +889,6 @@
         <v>1</v>
       </c>
       <c r="F11" s="2">
-        <f>SUM($E$4:$E11)</f>
         <v>10</v>
       </c>
       <c r="G11" s="2">
@@ -920,11 +907,9 @@
         <v>830.6</v>
       </c>
       <c r="L11" s="2">
-        <f>$K$11*30</f>
         <v>24918</v>
       </c>
       <c r="M11" s="2">
-        <f>ROUND($L$11/($J$11/3),0)</f>
         <v>21</v>
       </c>
     </row>
@@ -942,7 +927,6 @@
         <v>1</v>
       </c>
       <c r="F12" s="2">
-        <f>SUM($E$4:$E12)</f>
         <v>11</v>
       </c>
       <c r="G12" s="2">
@@ -961,11 +945,9 @@
         <v>911.1</v>
       </c>
       <c r="L12" s="2">
-        <f>$K$12*30</f>
         <v>27333</v>
       </c>
       <c r="M12" s="2">
-        <f>ROUND($L$12/($J$12/3),0)</f>
         <v>22</v>
       </c>
     </row>
@@ -983,7 +965,6 @@
         <v>1</v>
       </c>
       <c r="F13" s="2">
-        <f>SUM($E$4:$E13)</f>
         <v>12</v>
       </c>
       <c r="G13" s="2">
@@ -1002,11 +983,9 @@
         <v>997.8</v>
       </c>
       <c r="L13" s="2">
-        <f>$K$13*30</f>
         <v>29934</v>
       </c>
       <c r="M13" s="2">
-        <f>ROUND($L$13/($J$13/3),0)</f>
         <v>24</v>
       </c>
     </row>
@@ -1024,7 +1003,6 @@
         <v>1</v>
       </c>
       <c r="F14" s="2">
-        <f>SUM($E$4:$E14)</f>
         <v>13</v>
       </c>
       <c r="G14" s="2">
@@ -1043,11 +1021,9 @@
         <v>1091</v>
       </c>
       <c r="L14" s="2">
-        <f>$K$14*30</f>
         <v>32730</v>
       </c>
       <c r="M14" s="2">
-        <f>ROUND($L$14/($J$14/3),0)</f>
         <v>25</v>
       </c>
     </row>
@@ -1065,7 +1041,6 @@
         <v>1</v>
       </c>
       <c r="F15" s="2">
-        <f>SUM($E$4:$E15)</f>
         <v>14</v>
       </c>
       <c r="G15" s="2">
@@ -1084,11 +1059,9 @@
         <v>1191.0999999999999</v>
       </c>
       <c r="L15" s="2">
-        <f>$K$15*30</f>
         <v>35733</v>
       </c>
       <c r="M15" s="2">
-        <f>ROUND($L$15/($J$15/3),0)</f>
         <v>26</v>
       </c>
     </row>
@@ -1106,7 +1079,6 @@
         <v>1</v>
       </c>
       <c r="F16" s="2">
-        <f>SUM($E$4:$E16)</f>
         <v>15</v>
       </c>
       <c r="G16" s="2">
@@ -1125,11 +1097,9 @@
         <v>1298.4000000000001</v>
       </c>
       <c r="L16" s="2">
-        <f>$K$16*30</f>
         <v>38952</v>
       </c>
       <c r="M16" s="2">
-        <f>ROUND($L$16/($J$16/3),0)</f>
         <v>28</v>
       </c>
     </row>
@@ -1147,7 +1117,6 @@
         <v>1</v>
       </c>
       <c r="F17" s="2">
-        <f>SUM($E$4:$E17)</f>
         <v>16</v>
       </c>
       <c r="G17" s="2">
@@ -1166,11 +1135,9 @@
         <v>1413.4</v>
       </c>
       <c r="L17" s="2">
-        <f>$K$17*30</f>
         <v>42402</v>
       </c>
       <c r="M17" s="2">
-        <f>ROUND($L$17/($J$17/3),0)</f>
         <v>29</v>
       </c>
     </row>
@@ -1188,7 +1155,6 @@
         <v>1</v>
       </c>
       <c r="F18" s="2">
-        <f>SUM($E$4:$E18)</f>
         <v>17</v>
       </c>
       <c r="G18" s="2">
@@ -1207,11 +1173,9 @@
         <v>1536.6</v>
       </c>
       <c r="L18" s="2">
-        <f>$K$18*30</f>
         <v>46098</v>
       </c>
       <c r="M18" s="2">
-        <f>ROUND($L$18/($J$18/3),0)</f>
         <v>30</v>
       </c>
     </row>
@@ -1229,7 +1193,6 @@
         <v>1</v>
       </c>
       <c r="F19" s="2">
-        <f>SUM($E$4:$E19)</f>
         <v>18</v>
       </c>
       <c r="G19" s="2">
@@ -1248,11 +1211,9 @@
         <v>1668.4</v>
       </c>
       <c r="L19" s="2">
-        <f>$K$19*30</f>
         <v>50052</v>
       </c>
       <c r="M19" s="2">
-        <f>ROUND($L$19/($J$19/3),0)</f>
         <v>32</v>
       </c>
     </row>
@@ -1270,7 +1231,6 @@
         <v>0</v>
       </c>
       <c r="F20" s="2">
-        <f>SUM($E$4:$E20)</f>
         <v>18</v>
       </c>
       <c r="G20" s="2">
@@ -1289,11 +1249,9 @@
         <v>1668.4</v>
       </c>
       <c r="L20" s="2">
-        <f>$K$20*30</f>
         <v>50052</v>
       </c>
       <c r="M20" s="2">
-        <f>ROUND($L$20/($J$20/3),0)</f>
         <v>32</v>
       </c>
     </row>
@@ -1311,7 +1269,6 @@
         <v>1</v>
       </c>
       <c r="F21" s="2">
-        <f>SUM($E$4:$E21)</f>
         <v>19</v>
       </c>
       <c r="G21" s="2">
@@ -1330,11 +1287,9 @@
         <v>1809.4</v>
       </c>
       <c r="L21" s="2">
-        <f>$K$21*30</f>
         <v>54282</v>
       </c>
       <c r="M21" s="2">
-        <f>ROUND($L$21/($J$21/3),0)</f>
         <v>33</v>
       </c>
     </row>
@@ -1352,7 +1307,6 @@
         <v>1</v>
       </c>
       <c r="F22" s="2">
-        <f>SUM($E$4:$E22)</f>
         <v>20</v>
       </c>
       <c r="G22" s="2">
@@ -1371,11 +1325,9 @@
         <v>1960</v>
       </c>
       <c r="L22" s="2">
-        <f>$K$22*30</f>
         <v>58800</v>
       </c>
       <c r="M22" s="2">
-        <f>ROUND($L$22/($J$22/3),0)</f>
         <v>35</v>
       </c>
     </row>
@@ -1393,7 +1345,6 @@
         <v>1</v>
       </c>
       <c r="F23" s="2">
-        <f>SUM($E$4:$E23)</f>
         <v>21</v>
       </c>
       <c r="G23" s="2">
@@ -1412,17 +1363,14 @@
         <v>2120.8000000000002</v>
       </c>
       <c r="L23" s="2">
-        <f>$K$23*30</f>
         <v>63624.000000000007</v>
       </c>
       <c r="M23" s="2">
-        <f>ROUND($L$23/($J$23/3),0)</f>
         <v>37</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>